--- a/forms/trg/Formulir_TRG_lsfa-trg.xlsx
+++ b/forms/trg/Formulir_TRG_lsfa-trg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B30)</f>
+        <f>COUNTA(Anggota!B5:B31)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F30)</f>
+        <f>COUNTA(Anggota!F5:F31)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,31 +913,39 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Syafiuddin, M.Si.</t>
+          <t>Prof. Dr. Ir. Najamuddin, M.Sc</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Budidaya Laut</t>
+          <t>Fishing Gear Design and Technology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-4737-0781</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>5976611</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57204369646</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -950,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Jamaluddin Jompa, M.Sc.</t>
+          <t>Dr. Ir. Syafiuddin, M.Si.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,28 +973,16 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Marine ecology and coral reef</t>
+          <t>Budidaya Laut</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-9740-333X</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>258630</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>6603032552</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -999,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Budimawan, DEA</t>
+          <t>Prof. Dr. Ir. Jamaluddin Jompa, M.Sc.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1014,7 +1010,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Fisheries Biology and Management</t>
+          <t>Marine ecology and coral reef</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1023,17 +1019,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0566-2305</t>
+          <t>0000-0001-9740-333X</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6005334</t>
+          <t>258630</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>7409768808</t>
+          <t>6603032552</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,12 +1044,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. M. Rijal Idrus, M.Sc</t>
+          <t>Prof. Dr. Ir. Budimawan, DEA</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1063,7 +1059,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Climate change, marine conservation</t>
+          <t>Fisheries Biology and Management</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1072,17 +1068,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4544-9162</t>
+          <t>0000-0003-0566-2305</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6679640</t>
+          <t>6005334</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>59478129600</t>
+          <t>7409768808</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1097,12 +1093,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Widyastuti, S.Kel</t>
+          <t>Dr. Ir. M. Rijal Idrus, M.Sc</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1112,7 +1108,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Genetic Diversity</t>
+          <t>Climate change, marine conservation</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1121,17 +1117,17 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0763-6581</t>
+          <t>0000-0003-4544-9162</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6782473</t>
+          <t>6679640</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57200720560</t>
+          <t>59478129600</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1146,12 +1142,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Kasri, S.Pi., M.Si.</t>
+          <t>Dr. Widyastuti, S.Kel</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1161,22 +1157,26 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Fisheries Socio-Economics</t>
+          <t>Genetic Diversity</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0763-6581</t>
+        </is>
+      </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6784301</t>
+          <t>6782473</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57212930685</t>
+          <t>57200720560</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1191,22 +1191,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Jesmond Sammut, Ph.D</t>
+          <t>Kasri, S.Pi., M.Si.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>The University of New South Wales, Sydney, Australia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Aquaculture</t>
+          <t>Fisheries Socio-Economics</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1214,10 +1214,14 @@
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6784301</t>
+        </is>
+      </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>6603405984</t>
+          <t>57212930685</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1232,37 +1236,33 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Bayu Priyambodo, Ph.D</t>
+          <t>Prof. Jesmond Sammut, Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Balai Budidaya Laut Lombok</t>
+          <t>The University of New South Wales, Sydney, Australia</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Aquaculture Analyst</t>
+          <t>Aquaculture</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-3487-2179%20</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>56556848400</t>
+          <t>6603405984</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1277,27 +1277,39 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Mateus Salvador</t>
+          <t>Bayu Priyambodo, Ph.D</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="n"/>
+          <t>Balai Budidaya Laut Lombok</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Aquaculture Analyst</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-3487-2179%20</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>56556848400</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1310,12 +1322,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Muh. Fauzan</t>
+          <t>Mateus Salvador</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1323,11 +1335,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Fishing Technology</t>
-        </is>
-      </c>
+      <c r="E14" s="11" t="n"/>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1347,12 +1355,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Femiliani Novita Sari</t>
+          <t>Muh. Fauzan</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1360,17 +1368,17 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Fishing Technology</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
-      <c r="K15" s="11" t="inlineStr">
-        <is>
-          <t>6782883</t>
-        </is>
-      </c>
+      <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
       <c r="M15" s="11" t="inlineStr">
         <is>
@@ -1384,12 +1392,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Nurul Eka Wijayanti Risa</t>
+          <t>Femiliani Novita Sari</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1403,7 +1411,11 @@
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>6782883</t>
+        </is>
+      </c>
       <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
@@ -1417,12 +1429,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Siskawati</t>
+          <t>Nurul Eka Wijayanti Risa</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1430,11 +1442,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Fishing Gear Technology</t>
-        </is>
-      </c>
+      <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1454,12 +1462,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Sunarti</t>
+          <t>Siskawati</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1489,10 +1497,26 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Sunarti</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Fishing Gear Technology</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>The Lobster Research Group focuses on the development, cultivation, and sustainable management of lobster fisheries in Indonesia. With an interdisciplinary approach, we integrate marine biology, aquaculture technology, and socio-economic studies to support the sustainable use of lobster resources. Our mission is to produce innovative research, provide scientific recommendations, and contribute to policy development and community empowerment. By collaborating with academic institutions, government, and industry, we strive to advance knowledge and promote responsible lobster aquaculture practices that benefit both the environment and coastal communities.</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1500,7 +1524,11 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1689,15 +1717,32 @@
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="12" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
